--- a/main/ig/ValueSet-eclaire-study-population-vs.xlsx
+++ b/main/ig/ValueSet-eclaire-study-population-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T15:44:45+00:00</t>
+    <t>2025-11-27T10:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-eclaire-study-population-vs.xlsx
+++ b/main/ig/ValueSet-eclaire-study-population-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T10:20:46+00:00</t>
+    <t>2025-11-27T15:06:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
